--- a/data/可用测点含义.xlsx
+++ b/data/可用测点含义.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\29224\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\29224\Desktop\TS_GC\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1122F881-15CD-4133-962C-5C430AC78BC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DC82945-C297-4F32-8386-7C7E5E0587B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="100">
   <si>
     <t>AR1410B.PV</t>
   </si>
@@ -367,6 +367,10 @@
   </si>
   <si>
     <t>沉降器中部温度</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -735,7 +739,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C55"/>
+  <dimension ref="A1:H55"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.109375" customWidth="1"/>
@@ -872,7 +876,7 @@
       </c>
       <c r="B16" s="8"/>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>15</v>
       </c>
@@ -880,7 +884,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>16</v>
       </c>
@@ -888,15 +892,18 @@
         <v>56</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B19" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="H19" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>18</v>
       </c>
@@ -904,13 +911,13 @@
         <v>57</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B21" s="8"/>
     </row>
-    <row r="22" spans="1:2" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
         <v>20</v>
       </c>
@@ -918,7 +925,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>21</v>
       </c>
@@ -926,7 +933,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>22</v>
       </c>
@@ -934,7 +941,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>23</v>
       </c>
@@ -942,7 +949,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>24</v>
       </c>
@@ -950,7 +957,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="27" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>25</v>
       </c>
@@ -958,7 +965,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="28" spans="1:2" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
         <v>26</v>
       </c>
@@ -966,7 +973,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>27</v>
       </c>
@@ -974,12 +981,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>29</v>
       </c>
@@ -987,7 +994,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>30</v>
       </c>
@@ -1030,6 +1037,9 @@
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>59</v>
+      </c>
+      <c r="B37" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">

--- a/data/可用测点含义.xlsx
+++ b/data/可用测点含义.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\29224\Desktop\TS_GC\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DC82945-C297-4F32-8386-7C7E5E0587B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0406C070-38CC-4CC1-873E-53C1BC803BCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-3105" windowWidth="16440" windowHeight="28320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="123">
   <si>
     <t>AR1410B.PV</t>
   </si>
@@ -358,10 +358,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>C提升管水平段温度记录控制</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>沉降器顶部油气出口温度</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -371,6 +367,102 @@
   </si>
   <si>
     <t xml:space="preserve"> </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CCSFI1401A、B、C</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>XIC1403</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>主风机风量，B、C是冗余</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>主风机流量控制阀门</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PI1101.PV</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PRCA1101B.PV</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>再生器顶部压力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>再生器顶部压力双动滑阀</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>再生器总藏量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FI1110</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>至沉降器的主风流量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>至外取热主风流量记录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>主风和增压一样</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FI1111</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FI1112</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>至外取热主风流量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TI1135.PV</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>外取热器温度指示，上层</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>副提升管水平段温度记录控制</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TV1101</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>主提升管再生滑阀</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TV1155</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>副提升管再生滑阀</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WRA1103.PV</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -739,11 +831,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H55"/>
+  <dimension ref="A1:H66"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.109375" customWidth="1"/>
     <col min="2" max="2" width="41.77734375" customWidth="1"/>
+    <col min="4" max="4" width="16.21875" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
   </cols>
   <sheetData>
@@ -900,7 +993,7 @@
         <v>55</v>
       </c>
       <c r="H19" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -1119,64 +1212,155 @@
         <v>44</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>94</v>
+        <v>116</v>
       </c>
     </row>
     <row r="48" spans="1:2" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
-        <v>45</v>
+        <v>115</v>
       </c>
       <c r="B48" s="7" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B49" s="8" t="s">
-        <v>95</v>
+    <row r="49" spans="1:2" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B49" s="7" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B50" s="8"/>
+        <v>46</v>
+      </c>
+      <c r="B50" s="8" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B51" s="8"/>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B52" t="s">
-        <v>96</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="B52" s="8"/>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B53" t="s">
-        <v>97</v>
+        <v>117</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B54" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B55" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B56" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B57" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
         <v>52</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B59" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B60" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B61" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B62" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B63" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B64" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B65" t="s">
+        <v>110</v>
+      </c>
+      <c r="D65" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B66" t="s">
+        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -1184,7 +1368,7 @@
     <mergeCell ref="C3:C8"/>
     <mergeCell ref="B20:B21"/>
     <mergeCell ref="B15:B16"/>
-    <mergeCell ref="B49:B51"/>
+    <mergeCell ref="B50:B52"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/可用测点含义.xlsx
+++ b/data/可用测点含义.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\29224\Desktop\TS_GC\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0406C070-38CC-4CC1-873E-53C1BC803BCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3BAFE6F-ED55-4B67-A795-DDA761969D92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-3105" windowWidth="16440" windowHeight="28320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="125">
   <si>
     <t>AR1410B.PV</t>
   </si>
@@ -463,6 +463,14 @@
   </si>
   <si>
     <t>WRA1103.PV</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FRC和FI都是流量控制</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>后缀RCA和I其实是一样的，比如LRCA1101和LI1101</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -831,13 +839,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H66"/>
+  <dimension ref="A1:G66"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.109375" customWidth="1"/>
     <col min="2" max="2" width="41.77734375" customWidth="1"/>
     <col min="4" max="4" width="16.21875" customWidth="1"/>
-    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="5" max="5" width="55.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -969,7 +977,7 @@
       </c>
       <c r="B16" s="8"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>15</v>
       </c>
@@ -977,7 +985,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>16</v>
       </c>
@@ -985,18 +993,21 @@
         <v>56</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B19" t="s">
         <v>55</v>
       </c>
-      <c r="H19" t="s">
+      <c r="E19" t="s">
+        <v>123</v>
+      </c>
+      <c r="G19" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>18</v>
       </c>
@@ -1004,13 +1015,13 @@
         <v>57</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B21" s="8"/>
     </row>
-    <row r="22" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
         <v>20</v>
       </c>
@@ -1018,7 +1029,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>21</v>
       </c>
@@ -1026,15 +1037,18 @@
         <v>73</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B24" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E24" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>23</v>
       </c>
@@ -1042,7 +1056,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>24</v>
       </c>
@@ -1050,7 +1064,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="27" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>25</v>
       </c>
@@ -1058,7 +1072,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="28" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
         <v>26</v>
       </c>
@@ -1066,7 +1080,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>27</v>
       </c>
@@ -1074,12 +1088,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>29</v>
       </c>
@@ -1087,7 +1101,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>30</v>
       </c>

--- a/data/可用测点含义.xlsx
+++ b/data/可用测点含义.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\29224\Desktop\TS_GC\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3BAFE6F-ED55-4B67-A795-DDA761969D92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73B405BB-47F4-42A9-8530-AF697BF61252}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-3105" windowWidth="16440" windowHeight="28320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="127">
   <si>
     <t>AR1410B.PV</t>
   </si>
@@ -471,6 +471,14 @@
   </si>
   <si>
     <t>后缀RCA和I其实是一样的，比如LRCA1101和LI1101</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>外取热流化风调节阀</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FRCA1111.MV</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -839,7 +847,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G66"/>
+  <dimension ref="A1:G67"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.109375" customWidth="1"/>
@@ -1039,341 +1047,349 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>22</v>
+        <v>126</v>
       </c>
       <c r="B24" t="s">
-        <v>74</v>
-      </c>
-      <c r="E24" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>75</v>
+        <v>74</v>
+      </c>
+      <c r="E25" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B26" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B27" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="27" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
+    <row r="28" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B28" s="3" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="28" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="6" t="s">
+    <row r="29" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B28" s="7" t="s">
+      <c r="B29" s="7" t="s">
         <v>77</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B29" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
+      </c>
+      <c r="B30" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B31" t="s">
-        <v>79</v>
+        <v>28</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="B38" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B39" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B40" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B41" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B42" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B43" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B44" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B45" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B46" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B47" t="s">
         <v>93</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B47" s="7" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="48" spans="1:2" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
-        <v>115</v>
+        <v>44</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>94</v>
+        <v>116</v>
       </c>
     </row>
     <row r="49" spans="1:2" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="6" t="s">
-        <v>45</v>
+        <v>115</v>
       </c>
       <c r="B49" s="7" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B50" s="8" t="s">
-        <v>95</v>
+    <row r="50" spans="1:2" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B50" s="7" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B51" s="8"/>
+        <v>46</v>
+      </c>
+      <c r="B51" s="8" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B52" s="8"/>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B53" t="s">
-        <v>117</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="B53" s="8"/>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B54" t="s">
-        <v>96</v>
+        <v>117</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B55" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>118</v>
+        <v>51</v>
       </c>
       <c r="B56" t="s">
-        <v>119</v>
+        <v>97</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B57" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>52</v>
+        <v>120</v>
+      </c>
+      <c r="B58" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="B59" t="s">
-        <v>101</v>
+        <v>52</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B60" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B61" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B62" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="B63" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="B64" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B65" t="s">
-        <v>110</v>
-      </c>
-      <c r="D65" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B66" t="s">
+        <v>110</v>
+      </c>
+      <c r="D66" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B67" t="s">
         <v>109</v>
       </c>
     </row>
@@ -1382,7 +1398,7 @@
     <mergeCell ref="C3:C8"/>
     <mergeCell ref="B20:B21"/>
     <mergeCell ref="B15:B16"/>
-    <mergeCell ref="B50:B52"/>
+    <mergeCell ref="B51:B53"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
